--- a/docs/道路参数.xlsx
+++ b/docs/道路参数.xlsx
@@ -1,179 +1,4298 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="11655" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+  <si>
+    <r>
+      <t>TARGET_CRS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF9E94D5"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"EPSG:4547"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 目标坐标系</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ROAD_LINK_GAP_TOLERANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 道路链接间隙容差</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MIN_CONNECTOR_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 最小连接长度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BRIDGE_ELEVATION_GROUP_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 桥梁高程分组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CIM3_PLAN_ACCURACY_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 规划精度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CIM3_HEIGHT_ACCURACY_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 高度精度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CIM3_MIN_GEOMETRIC_DETAIL_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 最小几何细节</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ELEVATION_SAMPLE_INTERVAL_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 高程采样间隔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SWEEP_SAMPLE_INTERVAL_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 扫掠采样间隔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DEFAULT_GROUND_ELEVATION_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 默认地面高程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DEM_MIN_VALID_ELEVATION_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>50.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># DEM最小有效高程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DEM_MAX_VALID_ELEVATION_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>300.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># DEM最大有效高程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ENABLE_DEM_ELEVATION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 启用DEM高程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FLAT_TOPOLOGY_TILE_SIZE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3500.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 平坦拓扑瓦片大小</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>STUDY_AREA_RADIUS_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 研究区域半径</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CROWN_SLOPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 冠层斜率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_CROWN_SLOPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道冠层斜率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_NODE_TOLERANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口节点容差</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_RADIUS_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口半径</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_CLIP_EXTRA_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口剪裁额外距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MIN_JUNCTION_CLIP_DISTANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 最小路口剪裁距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MAX_JUNCTION_CLIP_DISTANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 最大路口剪裁距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_ENDPOINT_SNAP_TOLERANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口端点捕捉容差</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_LINE_INTERSECTION_TOLERANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口线交集容差</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ENABLE_CORRIDOR_JUNCTION_CLUSTERING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 启用路口聚类</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CORRIDOR_JUNCTION_CLUSTER_DISTANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>24.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口聚类距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CORRIDOR_JUNCTION_CONNECT_TOLERANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>18.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口聚类连接容差</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CORRIDOR_CROSSING_MIN_ANGLE_DEG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>25.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口交叉最小角度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CORRIDOR_CROSSING_EXTRA_WIDTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口交叉额外宽度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ROAD_SURFACE_OVERLAP_MIN_AREA_M2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>18.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路面重叠最小面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ROAD_SURFACE_OVERLAP_MIN_COMPACTNESS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.015</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路面重叠最小紧凑度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_EDGE_MAX_INTERSECTION_FACTOR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口边缘最大交集因子</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_MIN_SURFACE_AREA_M2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口最小表面面积</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_CLEAN_FILLET_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口清洁圆角</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_SOCKET_OVERLAP_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口socket重叠距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_CITYENGINE_SMOOTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口城市引擎平滑距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_MARKING_CLEARANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.65</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口标记清除距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_ASPHALT_ONLY_CLEARANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口沥青清除距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_ROAD_SURFACE_SETBACK_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口道路表面退让距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_CURB_SETBACK_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口路缘石退让距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_SIDEWALK_SETBACK_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口人行道退让距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_NON_ASPHALT_CLEARANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口非沥青清除距离</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_APPROACH_CONNECT_TOLERANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>22.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口接近连接容差</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JUNCTION_APPROACH_CONNECT_MAX_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>18.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口接近连接最大长度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_CONNECTOR_SAMPLE_COUNT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道连接采样数量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_CONNECTOR_HANDLE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道连接处理比例</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRANSITION_MIN_ANGLE_DEG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 过渡最小角度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRANSITION_MIN_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 过渡最小长度 4.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRANSITION_MAX_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>24.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 过渡最大长度 24.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TRANSITION_SAMPLES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 过渡采样数量 10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_GUIDE_MARKING_WIDTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道引导标记宽度 0.12米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DOUBLE_YELLOW_LINE_WIDTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 双黄线宽度 0.10米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>DOUBLE_YELLOW_LINE_OFFSET_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 双黄线偏移距离 0.12米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_DASH_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道虚线长度 5.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_DASH_GAP_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道虚线间隔 7.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LANE_DASH_MIN_ROAD_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>18.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道虚线最小道路长度 18.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TURN_ARROW_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 转向箭头长度 4.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GENERATE_TURN_ARROWS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 生成转向箭头</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>APPROACH_ARROW_NEAR_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 接近箭头近端距离 14.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>APPROACH_ARROW_FAR_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>27.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 接近箭头远端距离 27.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>APPROACH_ARROW_MIN_GAP_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 接近箭头最小间距 6.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CHANNELIZATION_MIN_ANGLE_DEG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>35.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 通道化最小角度 35.0度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CHANNELIZATION_MAX_ANGLE_DEG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>125.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 通道化最大角度 125.0度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CROSSWALK_DISTANCE_FROM_JUNCTION_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 人行横道距离路口距离 7.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CROSSWALK_STRIPE_WIDTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 人行横道条纹宽度 0.32米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CROSSWALK_STRIPE_GAP_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.42</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 人行横道条纹间隔 0.42米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CROSSWALK_BAND_LENGTH_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 人行横道带长度 3.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GENERATE_CROSSWALKS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 生成人行横道</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GENERATE_SWEPT_ROAD_SURFACES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 生成扫掠道路表面</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GENERATE_LANE_SURFACES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 生成车道表面</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TREE_JUNCTION_CLEARANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 树与路口的距离 20.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>STREET_LIGHT_JUNCTION_CLEARANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路灯与路口的距离 14.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>STREET_LIGHT_POLE_ROAD_CLEARANCE_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路灯杆与道路的距离 0.45米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MAX_STREET_LIGHTS_PER_ROAD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>800</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 每条道路最多800盏路灯</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MAX_TREES_PER_ROAD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>900</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 每条道路最多900棵树</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BRIDGE_PIER_SPACING_M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>28.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 桥梁桥墩间距 28.0米</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>GENERATE_JUNCTION_LABELS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>False</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 生成路口标签</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MIN_JUNCTION_QUALITY_SCORE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB8448B"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>85.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 路口质量评分最低85分</t>
+    </r>
+  </si>
+  <si>
+    <t>@dataclass</t>
+  </si>
+  <si>
+    <r>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>LaneSocket</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:  </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道socket</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    lane_socket_id: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道socketID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    parent_socket_id: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 父socketID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    road_id: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 道路ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    lane_index: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道索引</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    lane_role: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道角色</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    center: tuple[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 中心点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    tangent: tuple[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 切线</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    normal: tuple[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 法线</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    lane_width: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>float</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道宽度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    allowed_movements: list[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 允许移动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    lane_id: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF9E94D5"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>""</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 车道ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    movement: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF9E94D5"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"through"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 移动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    allowed_turns: list[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFB3003F"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF206595"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>None</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 允许转向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    traffic_direction: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF9E94D5"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"unknown"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 交通方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    signal_group: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF9E94D5"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"unsignalized"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 信号组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    stop_control: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF6F9BA6"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>str</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF9E94D5"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>"yield_or_stop_line"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10.5"/>
+        <color rgb="FF141414"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t># 停止控制</t>
+    </r>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF1F8A65"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFB3003F"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF141414"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF206595"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFB8448B"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.5"/>
+      <color rgb="FF141414"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF6F9BA6"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF9E94D5"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,157 +4592,169 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -678,74 +4809,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +5065,525 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A78"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="58.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="69.75" spans="1:1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" ht="96.75" spans="1:1">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="82.5" spans="1:1">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" ht="82.5" spans="1:1">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="69.75" spans="1:1">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="69.75" spans="1:1">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="96.75" spans="1:1">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="96.75" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="82.5" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="84" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" ht="98.25" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="98.25" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" ht="84" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="96.75" spans="1:1">
+      <c r="A14" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" ht="82.5" spans="1:1">
+      <c r="A15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="55.5" spans="1:1">
+      <c r="A16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="69.75" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" ht="84" spans="1:1">
+      <c r="A18" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="69.75" spans="1:1">
+      <c r="A19" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" ht="82.5" spans="1:1">
+      <c r="A20" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" ht="96.75" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="96.75" spans="1:1">
+      <c r="A22" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" ht="111" spans="1:1">
+      <c r="A23" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" ht="111" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" ht="111" spans="1:1">
+      <c r="A25" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="111" spans="1:1">
+      <c r="A26" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" ht="111" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" ht="96.75" spans="1:1">
+      <c r="A28" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" ht="96.75" spans="1:1">
+      <c r="A29" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" ht="96.75" spans="1:1">
+      <c r="A30" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" ht="123.75" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="123.75" spans="1:1">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" ht="96.75" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" ht="82.5" spans="1:1">
+      <c r="A34" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" ht="98.25" spans="1:1">
+      <c r="A35" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" ht="109.5" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" ht="96.75" spans="1:1">
+      <c r="A37" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" ht="111" spans="1:1">
+      <c r="A38" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" ht="109.5" spans="1:1">
+      <c r="A39" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" ht="95.25" spans="1:1">
+      <c r="A40" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" ht="96.75" spans="1:1">
+      <c r="A41" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" ht="109.5" spans="1:1">
+      <c r="A42" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" ht="111" spans="1:1">
+      <c r="A43" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" ht="123.75" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" ht="96.75" spans="1:1">
+      <c r="A45" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" ht="96.75" spans="1:1">
+      <c r="A46" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" ht="82.5" spans="1:1">
+      <c r="A47" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" ht="96.75" spans="1:1">
+      <c r="A48" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" ht="98.25" spans="1:1">
+      <c r="A49" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" ht="85.5" spans="1:1">
+      <c r="A50" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" ht="112.5" spans="1:1">
+      <c r="A51" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" ht="111" spans="1:1">
+      <c r="A52" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" ht="112.5" spans="1:1">
+      <c r="A53" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" ht="85.5" spans="1:1">
+      <c r="A54" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" ht="82.5" spans="1:1">
+      <c r="A55" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" ht="125.25" spans="1:1">
+      <c r="A56" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" ht="84" spans="1:1">
+      <c r="A57" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" ht="82.5" spans="1:1">
+      <c r="A58" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" ht="98.25" spans="1:1">
+      <c r="A59" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" ht="98.25" spans="1:1">
+      <c r="A60" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" ht="98.25" spans="1:1">
+      <c r="A61" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" ht="112.5" spans="1:1">
+      <c r="A62" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" ht="112.5" spans="1:1">
+      <c r="A63" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" ht="126.75" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" ht="98.25" spans="1:1">
+      <c r="A65" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" ht="98.25" spans="1:1">
+      <c r="A66" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" ht="98.25" spans="1:1">
+      <c r="A67" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" ht="82.5" spans="1:1">
+      <c r="A68" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" ht="96.75" spans="1:1">
+      <c r="A69" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" ht="82.5" spans="1:1">
+      <c r="A70" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" ht="99.75" spans="1:1">
+      <c r="A71" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" ht="125.25" spans="1:1">
+      <c r="A72" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" ht="138" spans="1:1">
+      <c r="A73" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" ht="98.25" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" ht="84" spans="1:1">
+      <c r="A75" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" ht="98.25" spans="1:1">
+      <c r="A76" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" ht="84" spans="1:1">
+      <c r="A77" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" ht="111" spans="1:1">
+      <c r="A78" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" ht="69.75" spans="1:1">
+      <c r="A2" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" ht="84" spans="1:1">
+      <c r="A3" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" ht="84" spans="1:1">
+      <c r="A4" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" ht="57" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" ht="69.75" spans="1:1">
+      <c r="A6" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" ht="55.5" spans="1:1">
+      <c r="A7" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" ht="84" spans="1:1">
+      <c r="A8" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" ht="84" spans="1:1">
+      <c r="A9" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" ht="84" spans="1:1">
+      <c r="A10" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" ht="69.75" spans="1:1">
+      <c r="A11" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" ht="98.25" spans="1:1">
+      <c r="A12" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" ht="57" spans="1:1">
+      <c r="A13" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" ht="71.25" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" ht="112.5" spans="1:1">
+      <c r="A15" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" ht="98.25" spans="1:1">
+      <c r="A16" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" ht="98.25" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" ht="112.5" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>